--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C9D947-F074-4876-AB17-7D20CF2FF298}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Terraform Modules Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Terraform Modules Tracker'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Terraform Modules Tracker'!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1290,10 +1290,10 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1303,21 +1303,21 @@
         <v>69</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1327,13 +1327,13 @@
         <v>72</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3"/>
     </row>

--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C9D947-F074-4876-AB17-7D20CF2FF298}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CABE8400-C94C-4BC3-9F97-536E8895B13F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -456,7 +456,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,6 +478,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,13 +515,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1532,10 +1539,10 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>103</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -1545,21 +1552,21 @@
         <v>105</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -1569,13 +1576,13 @@
         <v>108</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H31" s="3"/>
     </row>
@@ -1604,7 +1611,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="6" t="s">
         <v>113</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -1628,7 +1635,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="6" t="s">
         <v>117</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -1676,7 +1683,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="6" t="s">
         <v>125</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -1700,7 +1707,7 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="6" t="s">
         <v>129</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -1724,7 +1731,7 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="6" t="s">
         <v>133</v>
       </c>
       <c r="B38" s="3" t="s">

--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CABE8400-C94C-4BC3-9F97-536E8895B13F}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47E45865-DF43-4BC7-BCBE-D5981F8A2349}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1225,10 +1225,10 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1238,21 +1238,21 @@
         <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1262,13 +1262,13 @@
         <v>62</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3"/>
     </row>

--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47E45865-DF43-4BC7-BCBE-D5981F8A2349}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5BB8156-C9AF-40BD-B896-2C0B5F47F45E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="138">
   <si>
     <t>Category</t>
   </si>
@@ -434,6 +434,9 @@
   </si>
   <si>
     <t>Check open SGs, public S3, unencrypted volumes</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1057,10 +1060,10 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1070,21 +1073,21 @@
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1094,13 +1097,13 @@
         <v>38</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H11" s="3"/>
     </row>
@@ -1419,10 +1422,10 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -1432,13 +1435,13 @@
         <v>87</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H25" s="3"/>
     </row>

--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5BB8156-C9AF-40BD-B896-2C0B5F47F45E}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44F62269-4799-482F-AADD-65193D07DC51}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1398,7 +1398,7 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1518,10 +1518,10 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -1590,10 +1590,10 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -1758,6 +1758,7 @@
       <c r="H38" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/terraform_modules_service_tracker V1.1.xlsx
+++ b/terraform_modules_service_tracker V1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ingrammicro-my.sharepoint.com/personal/jeetendra_wadhwani_ingrammicro_com/Documents/Desktop/terraform-aws-delivery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44F62269-4799-482F-AADD-65193D07DC51}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{F7EB1B05-2536-42C3-822D-4580F810F1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B53C5C78-F2AC-4B37-A344-DC4437AC391B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1108,10 +1108,10 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1121,13 +1121,13 @@
         <v>41</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H12" s="3"/>
     </row>
